--- a/IV Sem/Docs/324DV.xlsx
+++ b/IV Sem/Docs/324DV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a1216fa42ee05d0/Documents/Training/LPU/Even 26/Docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a1216fa42ee05d0/Documents/Training/LPU/Even 26/K24DV/IV Sem/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7632C1C-B7AB-42C5-84E2-D1422005EF73}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B8FF9D39-8169-40B0-83B1-8BE3AF46D171}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="14664" windowHeight="12336" activeTab="1" xr2:uid="{B8FF9D39-8169-40B0-83B1-8BE3AF46D171}"/>
   </bookViews>
   <sheets>
     <sheet name=" Semester 1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -69,9 +69,6 @@
     <t>Chakka Chinni Krishna</t>
   </si>
   <si>
-    <t xml:space="preserve">	7002921076</t>
-  </si>
-  <si>
     <t>M Tarunesh</t>
   </si>
   <si>
@@ -79,6 +76,60 @@
   </si>
   <si>
     <t>GitHub</t>
+  </si>
+  <si>
+    <t>https://github.com/GrayViper</t>
+  </si>
+  <si>
+    <t>tarunsarmosa@gmail.com</t>
+  </si>
+  <si>
+    <t>chakkaanil6@gmail.com</t>
+  </si>
+  <si>
+    <t>ranamehak567@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	8135839393</t>
+  </si>
+  <si>
+    <t>rimmib51@gmail.com</t>
+  </si>
+  <si>
+    <t>archishmansingh805@gmail.com</t>
+  </si>
+  <si>
+    <t>murlimanohar1098@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/Zlan9</t>
+  </si>
+  <si>
+    <t>https://github.com/MurliManoharKumar</t>
+  </si>
+  <si>
+    <t>Tinashe Prince Mukwena</t>
+  </si>
+  <si>
+    <t>princemukwena43@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/sreejithore</t>
+  </si>
+  <si>
+    <t>sreejit2006hore@gmail.com</t>
+  </si>
+  <si>
+    <t>github.com/rimmibhardwaj</t>
+  </si>
+  <si>
+    <t>github.com/mehakrana9876</t>
+  </si>
+  <si>
+    <t>https://github.com/4Prince-bot</t>
+  </si>
+  <si>
+    <t>https://github.com/TARUNNESH</t>
   </si>
 </sst>
 </file>
@@ -201,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -216,6 +267,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -233,6 +290,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -576,13 +637,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD78A7B4-195C-491B-A160-95C157F86BB6}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="39.77734375" style="8" customWidth="1"/>
     <col min="4" max="4" width="33.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -599,31 +661,41 @@
         <v>4</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="C2" s="8">
         <v>9395870223</v>
       </c>
       <c r="D2" s="6">
         <v>12406700</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="C3" s="8">
         <v>8397964471</v>
       </c>
       <c r="D3" s="6">
         <v>12401467</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -642,24 +714,34 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="6">
         <v>12408977</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="C6" s="8">
         <v>9236646407</v>
       </c>
       <c r="D6" s="6">
         <v>12415355</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -678,39 +760,88 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="C8" s="8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6">
         <v>12414298</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C9" s="8">
         <v>8939697358</v>
       </c>
       <c r="D9" s="6">
         <v>12405965</v>
       </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="C10" s="8">
         <v>7321814092</v>
       </c>
       <c r="D10" s="6">
         <v>12408716</v>
       </c>
+      <c r="E10" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="8">
+        <v>7347266968</v>
+      </c>
+      <c r="D11" s="10">
+        <v>12405267</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{C55E549B-3C22-455E-AD8F-00FD27828A09}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{FFAF6FE2-D34A-4DA3-855A-C8EF066A727A}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{7B36EFC8-B0EF-4E4A-8D5A-62CB2FE1904B}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{8964DEE8-B127-429F-A61F-566070230166}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{2508C25E-CFA5-4A04-A84E-F106064AE46F}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{1C5ACE6E-93E3-419C-BF81-291884C1035A}"/>
+    <hyperlink ref="B10" r:id="rId7" xr:uid="{9874DB8C-A901-405F-8223-0B8E0DB08B5E}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{B015EE02-8DE6-45BE-8B94-2D2FA9F8E9FE}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{BBC663A6-D432-468D-BDE4-D01BF277CF03}"/>
+    <hyperlink ref="B5" r:id="rId10" xr:uid="{8856A549-0A84-4180-A8AA-A0097E29FB9B}"/>
+    <hyperlink ref="E5" r:id="rId11" xr:uid="{407289A4-778D-41A8-96D7-8C3F417D9372}"/>
+    <hyperlink ref="B9" r:id="rId12" xr:uid="{FF895634-7740-4377-944C-72A2406EEA73}"/>
+    <hyperlink ref="E2" r:id="rId13" display="https://github.com/rimmibhardwaj" xr:uid="{A555EE4E-7799-4493-B485-6BECBA5141A0}"/>
+    <hyperlink ref="E11" r:id="rId14" xr:uid="{17A771A5-97BF-42B4-BB13-A47BBE1F39FE}"/>
+    <hyperlink ref="E9" r:id="rId15" xr:uid="{28228094-60C6-4C35-B8B3-4C4723B9F3F1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/IV Sem/Docs/324DV.xlsx
+++ b/IV Sem/Docs/324DV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a1216fa42ee05d0/Documents/Training/LPU/Even 26/K24DV/IV Sem/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7632C1C-B7AB-42C5-84E2-D1422005EF73}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A40AE6-79D1-42E9-8F9A-F002971280EB}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14664" windowHeight="12336" activeTab="1" xr2:uid="{B8FF9D39-8169-40B0-83B1-8BE3AF46D171}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="14664" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{B8FF9D39-8169-40B0-83B1-8BE3AF46D171}"/>
   </bookViews>
   <sheets>
     <sheet name=" Semester 1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,28 @@
     <sheet name="Semester 5" sheetId="3" r:id="rId3"/>
     <sheet name="Semster 7" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -45,66 +56,87 @@
     <t>Reg. No.</t>
   </si>
   <si>
+    <t>GitHub</t>
+  </si>
+  <si>
     <t>Rimmi Bhardwaj</t>
   </si>
   <si>
+    <t>rimmib51@gmail.com</t>
+  </si>
+  <si>
+    <t>github.com/rimmibhardwaj</t>
+  </si>
+  <si>
     <t>Mehak</t>
   </si>
   <si>
+    <t>ranamehak567@gmail.com</t>
+  </si>
+  <si>
+    <t>github.com/mehakrana9876</t>
+  </si>
+  <si>
     <t>Pathik Singh</t>
   </si>
   <si>
+    <t>singhpathik4002@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/PathikSingh</t>
+  </si>
+  <si>
     <t>Sreejit Hore</t>
   </si>
   <si>
+    <t>sreejit2006hore@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">	9142324405</t>
   </si>
   <si>
+    <t>https://github.com/sreejithore</t>
+  </si>
+  <si>
     <t>Archishman Singh</t>
   </si>
   <si>
+    <t>archishmansingh805@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/Zlan9</t>
+  </si>
+  <si>
     <t xml:space="preserve">	Keshav Saini</t>
   </si>
   <si>
     <t>Chakka Chinni Krishna</t>
   </si>
   <si>
+    <t>chakkaanil6@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	8135839393</t>
+  </si>
+  <si>
+    <t>https://github.com/GrayViper</t>
+  </si>
+  <si>
     <t>M Tarunesh</t>
   </si>
   <si>
+    <t>tarunsarmosa@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/TARUNNESH</t>
+  </si>
+  <si>
     <t>Murli Manohar Kumar</t>
   </si>
   <si>
-    <t>GitHub</t>
-  </si>
-  <si>
-    <t>https://github.com/GrayViper</t>
-  </si>
-  <si>
-    <t>tarunsarmosa@gmail.com</t>
-  </si>
-  <si>
-    <t>chakkaanil6@gmail.com</t>
-  </si>
-  <si>
-    <t>ranamehak567@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	8135839393</t>
-  </si>
-  <si>
-    <t>rimmib51@gmail.com</t>
-  </si>
-  <si>
-    <t>archishmansingh805@gmail.com</t>
-  </si>
-  <si>
     <t>murlimanohar1098@gmail.com</t>
   </si>
   <si>
-    <t>https://github.com/Zlan9</t>
-  </si>
-  <si>
     <t>https://github.com/MurliManoharKumar</t>
   </si>
   <si>
@@ -114,29 +146,14 @@
     <t>princemukwena43@gmail.com</t>
   </si>
   <si>
-    <t>https://github.com/sreejithore</t>
-  </si>
-  <si>
-    <t>sreejit2006hore@gmail.com</t>
-  </si>
-  <si>
-    <t>github.com/rimmibhardwaj</t>
-  </si>
-  <si>
-    <t>github.com/mehakrana9876</t>
-  </si>
-  <si>
     <t>https://github.com/4Prince-bot</t>
-  </si>
-  <si>
-    <t>https://github.com/TARUNNESH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,10 +307,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -614,9 +627,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCCD7A1-B771-48F6-892D-D4235813839B}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,16 +651,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD78A7B4-195C-491B-A160-95C157F86BB6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="33.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,15 +674,15 @@
         <v>4</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="13.9" customHeight="1">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C2" s="8">
         <v>9395870223</v>
@@ -678,15 +691,15 @@
         <v>12406700</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C3" s="8">
         <v>8397964471</v>
@@ -695,44 +708,49 @@
         <v>12401467</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="C4" s="8">
         <v>9151761127</v>
       </c>
       <c r="D4" s="6">
         <v>12406573</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6">
         <v>12408977</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8">
         <v>9236646407</v>
@@ -741,12 +759,12 @@
         <v>12415355</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8">
@@ -756,29 +774,29 @@
         <v>12403803</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8" s="6">
         <v>12414298</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C9" s="8">
         <v>8939697358</v>
@@ -787,15 +805,15 @@
         <v>12405965</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C10" s="8">
         <v>7321814092</v>
@@ -804,15 +822,15 @@
         <v>12408716</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.9">
       <c r="A11" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C11" s="8">
         <v>7347266968</v>
@@ -821,7 +839,7 @@
         <v>12405267</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -841,6 +859,8 @@
     <hyperlink ref="E2" r:id="rId13" display="https://github.com/rimmibhardwaj" xr:uid="{A555EE4E-7799-4493-B485-6BECBA5141A0}"/>
     <hyperlink ref="E11" r:id="rId14" xr:uid="{17A771A5-97BF-42B4-BB13-A47BBE1F39FE}"/>
     <hyperlink ref="E9" r:id="rId15" xr:uid="{28228094-60C6-4C35-B8B3-4C4723B9F3F1}"/>
+    <hyperlink ref="B4" r:id="rId16" xr:uid="{2912DA6D-7FA6-491B-94E6-0EF738321AEF}"/>
+    <hyperlink ref="E4" r:id="rId17" xr:uid="{F21BB858-C29E-43FB-A71B-ECD341E65CCA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -849,9 +869,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F215439-0DF9-4CF5-B74A-3CC6A2BFD47C}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,9 +893,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F8FB5F7-4A28-496B-8DE1-4DB5D3A593AA}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/IV Sem/Docs/324DV.xlsx
+++ b/IV Sem/Docs/324DV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a1216fa42ee05d0/Documents/Training/LPU/Even 26/K24DV/IV Sem/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A40AE6-79D1-42E9-8F9A-F002971280EB}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{FF6677E9-2713-4D78-ADDA-921602653D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D07BD38-36EB-4023-8DAD-A9A0133B1C81}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="14664" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{B8FF9D39-8169-40B0-83B1-8BE3AF46D171}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t xml:space="preserve">	Keshav Saini</t>
+  </si>
+  <si>
+    <t>saini.ks2710@gmail.com</t>
+  </si>
+  <si>
+    <t>https://github.com/Sainikeshav27234</t>
   </si>
   <si>
     <t>Chakka Chinni Krishna</t>
@@ -762,41 +768,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="C7" s="8">
         <v>9682106037</v>
       </c>
       <c r="D7" s="6">
         <v>12403803</v>
       </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6">
         <v>12414298</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8">
         <v>8939697358</v>
@@ -805,15 +816,15 @@
         <v>12405965</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" s="8">
         <v>7321814092</v>
@@ -822,15 +833,15 @@
         <v>12408716</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.9">
       <c r="A11" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="8">
         <v>7347266968</v>
@@ -839,7 +850,7 @@
         <v>12405267</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -861,6 +872,8 @@
     <hyperlink ref="E9" r:id="rId15" xr:uid="{28228094-60C6-4C35-B8B3-4C4723B9F3F1}"/>
     <hyperlink ref="B4" r:id="rId16" xr:uid="{2912DA6D-7FA6-491B-94E6-0EF738321AEF}"/>
     <hyperlink ref="E4" r:id="rId17" xr:uid="{F21BB858-C29E-43FB-A71B-ECD341E65CCA}"/>
+    <hyperlink ref="B7" r:id="rId18" xr:uid="{61326353-DF3F-47C1-9177-62E773FE4B52}"/>
+    <hyperlink ref="E7" r:id="rId19" xr:uid="{039580C3-E615-4618-A8F0-5567741CE329}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
